--- a/Team-Data/2015-16/4-11-2015-16.xlsx
+++ b/Team-Data/2015-16/4-11-2015-16.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -679,7 +746,7 @@
         <v>38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.458</v>
@@ -688,7 +755,7 @@
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="N2" t="n">
         <v>0.351</v>
@@ -700,7 +767,7 @@
         <v>19.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.783</v>
+        <v>0.786</v>
       </c>
       <c r="R2" t="n">
         <v>8.300000000000001</v>
@@ -709,7 +776,7 @@
         <v>33.8</v>
       </c>
       <c r="T2" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U2" t="n">
         <v>25.7</v>
@@ -721,10 +788,10 @@
         <v>9.1</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
         <v>19.1</v>
@@ -739,7 +806,7 @@
         <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -751,7 +818,7 @@
         <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>8</v>
@@ -766,10 +833,10 @@
         <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -778,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>25</v>
@@ -799,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -846,13 +913,13 @@
         <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.575</v>
+        <v>0.588</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -864,7 +931,7 @@
         <v>89.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
         <v>8.800000000000001</v>
@@ -876,13 +943,13 @@
         <v>0.335</v>
       </c>
       <c r="O3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P3" t="n">
         <v>23.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.785</v>
+        <v>0.786</v>
       </c>
       <c r="R3" t="n">
         <v>11.6</v>
@@ -894,46 +961,46 @@
         <v>45</v>
       </c>
       <c r="U3" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y3" t="n">
         <v>5.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>7</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>12</v>
@@ -951,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
         <v>10</v>
@@ -960,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>3</v>
@@ -981,13 +1048,13 @@
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -1046,28 +1113,28 @@
         <v>84.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O4" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R4" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
         <v>31.9</v>
@@ -1076,7 +1143,7 @@
         <v>42.4</v>
       </c>
       <c r="U4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V4" t="n">
         <v>14.9</v>
@@ -1085,7 +1152,7 @@
         <v>7.6</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y4" t="n">
         <v>5.2</v>
@@ -1094,16 +1161,16 @@
         <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC4" t="n">
         <v>-7.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>28</v>
@@ -1118,10 +1185,10 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>13</v>
@@ -1145,7 +1212,7 @@
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
         <v>26</v>
@@ -1163,7 +1230,7 @@
         <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -1210,40 +1277,40 @@
         <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.588</v>
+        <v>0.575</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J5" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O5" t="n">
         <v>18.8</v>
       </c>
       <c r="P5" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0.792</v>
@@ -1252,22 +1319,22 @@
         <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="T5" t="n">
         <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
         <v>12.6</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
@@ -1276,34 +1343,34 @@
         <v>18.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>103.4</v>
+        <v>103.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH5" t="n">
         <v>8</v>
       </c>
-      <c r="AF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9</v>
-      </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
         <v>7</v>
@@ -1324,10 +1391,10 @@
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>4</v>
@@ -1348,10 +1415,10 @@
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1456,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J6" t="n">
         <v>87.59999999999999</v>
@@ -1419,31 +1486,31 @@
         <v>21.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O6" t="n">
         <v>16.4</v>
       </c>
       <c r="P6" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="R6" t="n">
         <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T6" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="U6" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="V6" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W6" t="n">
         <v>6</v>
@@ -1452,37 +1519,37 @@
         <v>5.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA6" t="n">
         <v>18.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.4</v>
+        <v>101.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
         <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
         <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ6" t="n">
         <v>2</v>
@@ -1491,7 +1558,7 @@
         <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM6" t="n">
         <v>24</v>
@@ -1500,16 +1567,16 @@
         <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
         <v>26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>3</v>
@@ -1518,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
@@ -1530,19 +1597,19 @@
         <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
         <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
         <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.709</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,10 +1656,10 @@
         <v>38.6</v>
       </c>
       <c r="J7" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L7" t="n">
         <v>10.8</v>
@@ -1604,31 +1671,31 @@
         <v>0.362</v>
       </c>
       <c r="O7" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P7" t="n">
         <v>21.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.75</v>
+        <v>0.746</v>
       </c>
       <c r="R7" t="n">
         <v>10.7</v>
       </c>
       <c r="S7" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T7" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U7" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.6</v>
       </c>
       <c r="W7" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X7" t="n">
         <v>3.8</v>
@@ -1637,19 +1704,19 @@
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA7" t="n">
         <v>20.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>104.4</v>
+        <v>104.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -1670,7 +1737,7 @@
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>2</v>
@@ -1679,28 +1746,28 @@
         <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP7" t="n">
         <v>24</v>
       </c>
-      <c r="AP7" t="n">
-        <v>23</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
@@ -1709,10 +1776,10 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>14</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -1768,43 +1835,43 @@
         <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O8" t="n">
         <v>17.7</v>
       </c>
       <c r="P8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S8" t="n">
         <v>33.9</v>
       </c>
       <c r="T8" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V8" t="n">
         <v>12.8</v>
@@ -1819,22 +1886,22 @@
         <v>4.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.3</v>
+        <v>102.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
@@ -1858,10 +1925,10 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>12</v>
@@ -1882,7 +1949,7 @@
         <v>19</v>
       </c>
       <c r="AU8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV8" t="n">
         <v>2</v>
@@ -1906,7 +1973,7 @@
         <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.407</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,28 +2020,28 @@
         <v>37.7</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L9" t="n">
         <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O9" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R9" t="n">
         <v>11.4</v>
@@ -1989,13 +2056,13 @@
         <v>22.6</v>
       </c>
       <c r="V9" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W9" t="n">
         <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" t="n">
         <v>6.3</v>
@@ -2010,37 +2077,37 @@
         <v>101.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
         <v>25</v>
@@ -2064,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
         <v>17</v>
@@ -2088,7 +2155,7 @@
         <v>19</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.526</v>
+        <v>0.538</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
         <v>86.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L10" t="n">
         <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.664</v>
+        <v>0.666</v>
       </c>
       <c r="R10" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S10" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T10" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="U10" t="n">
         <v>19.4</v>
@@ -2174,7 +2241,7 @@
         <v>13.5</v>
       </c>
       <c r="W10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X10" t="n">
         <v>3.6</v>
@@ -2186,25 +2253,25 @@
         <v>19.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB10" t="n">
         <v>102</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>8</v>
@@ -2216,7 +2283,7 @@
         <v>5</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
         <v>11</v>
@@ -2240,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
         <v>3</v>
@@ -2261,10 +2328,10 @@
         <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.888</v>
+        <v>0.889</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
@@ -2317,19 +2384,19 @@
         <v>42.5</v>
       </c>
       <c r="J11" t="n">
-        <v>87.2</v>
+        <v>87.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="L11" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="M11" t="n">
         <v>31.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.417</v>
+        <v>0.415</v>
       </c>
       <c r="O11" t="n">
         <v>16.7</v>
@@ -2338,22 +2405,22 @@
         <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S11" t="n">
         <v>36.2</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U11" t="n">
         <v>28.9</v>
       </c>
       <c r="V11" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W11" t="n">
         <v>8.4</v>
@@ -2362,13 +2429,13 @@
         <v>6.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
         <v>114.8</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2413,13 +2480,13 @@
         <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
         <v>16</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>9</v>
@@ -2440,13 +2507,13 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ11" t="n">
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -2484,34 +2551,34 @@
         <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J12" t="n">
         <v>83.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.453</v>
+        <v>0.45</v>
       </c>
       <c r="L12" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="M12" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
         <v>20.5</v>
@@ -2523,7 +2590,7 @@
         <v>0.695</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S12" t="n">
         <v>31.6</v>
@@ -2532,10 +2599,10 @@
         <v>42.9</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W12" t="n">
         <v>10</v>
@@ -2544,43 +2611,43 @@
         <v>5.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA12" t="n">
         <v>22.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.7</v>
+        <v>106.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
         <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,10 +2665,10 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
         <v>27</v>
@@ -2610,7 +2677,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>27</v>
@@ -2625,16 +2692,16 @@
         <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB12" t="n">
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
         <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J13" t="n">
         <v>85.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L13" t="n">
         <v>8.1</v>
@@ -2693,25 +2760,25 @@
         <v>23.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
         <v>33.9</v>
       </c>
       <c r="T13" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
@@ -2720,28 +2787,28 @@
         <v>14.9</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X13" t="n">
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -2762,7 +2829,7 @@
         <v>13</v>
       </c>
       <c r="AK13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
         <v>18</v>
@@ -2783,19 +2850,19 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
         <v>22</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>4</v>
@@ -2804,7 +2871,7 @@
         <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
         <v>11</v>
@@ -2816,7 +2883,7 @@
         <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
@@ -2866,13 +2933,13 @@
         <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="N14" t="n">
         <v>0.364</v>
@@ -2881,16 +2948,16 @@
         <v>18.3</v>
       </c>
       <c r="P14" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0.6909999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
         <v>42.1</v>
@@ -2899,31 +2966,31 @@
         <v>22.8</v>
       </c>
       <c r="V14" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y14" t="n">
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA14" t="n">
         <v>22.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2938,7 +3005,7 @@
         <v>10</v>
       </c>
       <c r="AI14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -2992,10 +3059,10 @@
         <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -3042,13 +3109,13 @@
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J15" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="L15" t="n">
         <v>7.8</v>
@@ -3060,16 +3127,16 @@
         <v>0.319</v>
       </c>
       <c r="O15" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R15" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S15" t="n">
         <v>32.1</v>
@@ -3078,34 +3145,34 @@
         <v>42.9</v>
       </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="V15" t="n">
         <v>13.7</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-9.9</v>
+        <v>-9.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>29</v>
@@ -3144,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3153,7 +3220,7 @@
         <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3168,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="AY15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ15" t="n">
         <v>13</v>
@@ -3177,7 +3244,7 @@
         <v>25</v>
       </c>
       <c r="BB15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -3209,43 +3276,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
         <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L16" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M16" t="n">
         <v>18.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.335</v>
+        <v>0.332</v>
       </c>
       <c r="O16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0.784</v>
@@ -3260,10 +3327,10 @@
         <v>41.7</v>
       </c>
       <c r="U16" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W16" t="n">
         <v>8.800000000000001</v>
@@ -3275,40 +3342,40 @@
         <v>5.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA16" t="n">
         <v>21.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
         <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3317,7 +3384,7 @@
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3326,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>8</v>
@@ -3350,7 +3417,7 @@
         <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ16" t="n">
         <v>27</v>
@@ -3362,7 +3429,7 @@
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -3391,52 +3458,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
         <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.582</v>
+        <v>0.588</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
         <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>0.336</v>
+        <v>0.339</v>
       </c>
       <c r="O17" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
         <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R17" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T17" t="n">
         <v>44.2</v>
@@ -3451,40 +3518,40 @@
         <v>6.8</v>
       </c>
       <c r="X17" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB17" t="n">
         <v>100.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF17" t="n">
         <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH17" t="n">
         <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AJ17" t="n">
         <v>27</v>
@@ -3499,31 +3566,31 @@
         <v>28</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>24</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
         <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
         <v>23</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>27</v>
@@ -3532,10 +3599,10 @@
         <v>1</v>
       </c>
       <c r="AY17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
@@ -3544,7 +3611,7 @@
         <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -3588,37 +3655,37 @@
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="J18" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.469</v>
+        <v>0.466</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
         <v>15.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.347</v>
       </c>
       <c r="O18" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P18" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.744</v>
+        <v>0.747</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T18" t="n">
         <v>41.6</v>
@@ -3627,31 +3694,31 @@
         <v>23.2</v>
       </c>
       <c r="V18" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB18" t="n">
         <v>99.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.9</v>
+        <v>-4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3663,10 +3730,10 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI18" t="n">
         <v>14</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
@@ -3681,7 +3748,7 @@
         <v>30</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>20</v>
@@ -3690,7 +3757,7 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
@@ -3705,7 +3772,7 @@
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>11</v>
@@ -3714,19 +3781,19 @@
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>25</v>
       </c>
       <c r="BC18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -3758,13 +3825,13 @@
         <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>0.338</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3785,16 +3852,16 @@
         <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O19" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P19" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.791</v>
+        <v>0.793</v>
       </c>
       <c r="R19" t="n">
         <v>10.1</v>
@@ -3812,28 +3879,28 @@
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y19" t="n">
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
@@ -3845,10 +3912,10 @@
         <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
         <v>28</v>
@@ -3863,7 +3930,7 @@
         <v>29</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
         <v>19</v>
@@ -3887,7 +3954,7 @@
         <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>14</v>
@@ -3896,7 +3963,7 @@
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
         <v>17</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="n">
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L20" t="n">
         <v>8.5</v>
@@ -3967,19 +4034,19 @@
         <v>23.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P20" t="n">
         <v>22.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R20" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S20" t="n">
         <v>33.3</v>
@@ -3988,10 +4055,10 @@
         <v>42.9</v>
       </c>
       <c r="U20" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
         <v>7.7</v>
@@ -4000,28 +4067,28 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z20" t="n">
         <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>102.8</v>
+        <v>102.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.1</v>
+        <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
         <v>25</v>
@@ -4030,34 +4097,34 @@
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
@@ -4066,16 +4133,16 @@
         <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
@@ -4084,13 +4151,13 @@
         <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
         <v>13</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
         <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.388</v>
+        <v>0.395</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K21" t="n">
         <v>0.439</v>
@@ -4149,25 +4216,25 @@
         <v>21.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O21" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.804</v>
       </c>
       <c r="R21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S21" t="n">
         <v>34.1</v>
       </c>
       <c r="T21" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U21" t="n">
         <v>20.4</v>
@@ -4176,31 +4243,31 @@
         <v>13.4</v>
       </c>
       <c r="W21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
         <v>4.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.2</v>
+        <v>98.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF21" t="n">
         <v>24</v>
@@ -4209,10 +4276,10 @@
         <v>24</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ21" t="n">
         <v>20</v>
@@ -4230,7 +4297,7 @@
         <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
         <v>25</v>
@@ -4239,19 +4306,19 @@
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
         <v>26</v>
       </c>
       <c r="AV21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW21" t="n">
         <v>30</v>
@@ -4263,10 +4330,10 @@
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -4319,67 +4386,67 @@
         <v>41.2</v>
       </c>
       <c r="J22" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L22" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
         <v>19.7</v>
       </c>
       <c r="P22" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.779</v>
+        <v>0.783</v>
       </c>
       <c r="R22" t="n">
         <v>13</v>
       </c>
       <c r="S22" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="T22" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="U22" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W22" t="n">
         <v>7.4</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
         <v>20.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB22" t="n">
         <v>110.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4391,13 +4458,13 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4406,7 +4473,7 @@
         <v>17</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN22" t="n">
         <v>17</v>
@@ -4418,7 +4485,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
         <v>1</v>
@@ -4439,16 +4506,16 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -4486,13 +4553,13 @@
         <v>80</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>0.438</v>
+        <v>0.425</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
@@ -4501,10 +4568,10 @@
         <v>39.5</v>
       </c>
       <c r="J23" t="n">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>7.8</v>
@@ -4513,55 +4580,55 @@
         <v>22.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P23" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R23" t="n">
         <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="U23" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="AC23" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
@@ -4573,7 +4640,7 @@
         <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>5</v>
@@ -4585,13 +4652,13 @@
         <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,37 +4673,37 @@
         <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
         <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
         <v>15</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
         <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>17</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4732,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" t="n">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J24" t="n">
         <v>84.09999999999999</v>
@@ -4692,7 +4759,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="N24" t="n">
         <v>0.335</v>
@@ -4704,31 +4771,31 @@
         <v>22.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="R24" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S24" t="n">
         <v>31.9</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X24" t="n">
         <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z24" t="n">
         <v>21.7</v>
@@ -4740,10 +4807,10 @@
         <v>97.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10</v>
+        <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4782,10 +4849,10 @@
         <v>19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
         <v>25</v>
@@ -4806,7 +4873,7 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ24" t="n">
         <v>25</v>
@@ -4815,7 +4882,7 @@
         <v>24</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -4862,10 +4929,10 @@
         <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K25" t="n">
         <v>0.435</v>
@@ -4880,13 +4947,13 @@
         <v>0.351</v>
       </c>
       <c r="O25" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P25" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R25" t="n">
         <v>11.4</v>
@@ -4898,7 +4965,7 @@
         <v>44.6</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V25" t="n">
         <v>17.2</v>
@@ -4910,7 +4977,7 @@
         <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z25" t="n">
         <v>22.7</v>
@@ -4919,13 +4986,13 @@
         <v>21.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>100.8</v>
+        <v>100.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4943,7 +5010,7 @@
         <v>23</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>28</v>
@@ -4958,16 +5025,16 @@
         <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
@@ -4982,13 +5049,13 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ25" t="n">
         <v>30</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0.525</v>
+        <v>0.531</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5050,7 +5117,7 @@
         <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
         <v>10.5</v>
@@ -5065,19 +5132,19 @@
         <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R26" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S26" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="T26" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U26" t="n">
         <v>21.3</v>
@@ -5101,58 +5168,58 @@
         <v>19.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>5</v>
@@ -5176,7 +5243,7 @@
         <v>26</v>
       </c>
       <c r="BA26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -5214,13 +5281,13 @@
         <v>80</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.413</v>
+        <v>0.4</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,40 +5296,40 @@
         <v>40.1</v>
       </c>
       <c r="J27" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L27" t="n">
         <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O27" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="R27" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S27" t="n">
         <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U27" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V27" t="n">
         <v>16.1</v>
@@ -5271,43 +5338,43 @@
         <v>8.9</v>
       </c>
       <c r="X27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB27" t="n">
         <v>106.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK27" t="n">
         <v>6</v>
@@ -5319,7 +5386,7 @@
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
@@ -5331,13 +5398,13 @@
         <v>26</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
         <v>4</v>
@@ -5352,13 +5419,13 @@
         <v>20</v>
       </c>
       <c r="AY27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
         <v>3</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E28" t="n">
         <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.823</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
@@ -5411,7 +5478,7 @@
         <v>40.2</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="K28" t="n">
         <v>0.485</v>
@@ -5420,16 +5487,16 @@
         <v>7</v>
       </c>
       <c r="M28" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="O28" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P28" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.804</v>
@@ -5441,10 +5508,10 @@
         <v>34.6</v>
       </c>
       <c r="T28" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U28" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V28" t="n">
         <v>13.1</v>
@@ -5465,13 +5532,13 @@
         <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5525,13 +5592,13 @@
         <v>3</v>
       </c>
       <c r="AV28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX28" t="n">
         <v>5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>6</v>
       </c>
       <c r="AY28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F29" t="n">
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5605,22 +5672,22 @@
         <v>23.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O29" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P29" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R29" t="n">
         <v>10.1</v>
       </c>
       <c r="S29" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T29" t="n">
         <v>43.1</v>
@@ -5629,13 +5696,13 @@
         <v>18.6</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y29" t="n">
         <v>5.4</v>
@@ -5644,25 +5711,25 @@
         <v>19.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>102.4</v>
+        <v>102.5</v>
       </c>
       <c r="AC29" t="n">
         <v>4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF29" t="n">
         <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
         <v>23</v>
@@ -5674,7 +5741,7 @@
         <v>29</v>
       </c>
       <c r="AK29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>14</v>
@@ -5692,13 +5759,13 @@
         <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR29" t="n">
         <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>18</v>
@@ -5707,7 +5774,7 @@
         <v>29</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
         <v>15</v>
@@ -5719,10 +5786,10 @@
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -5784,22 +5851,22 @@
         <v>8.5</v>
       </c>
       <c r="M30" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="N30" t="n">
         <v>0.357</v>
       </c>
       <c r="O30" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P30" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
         <v>32.5</v>
@@ -5808,7 +5875,7 @@
         <v>43.4</v>
       </c>
       <c r="U30" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5817,16 +5884,16 @@
         <v>7.7</v>
       </c>
       <c r="X30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB30" t="n">
         <v>97.8</v>
@@ -5835,7 +5902,7 @@
         <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5856,13 +5923,13 @@
         <v>30</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AN30" t="n">
         <v>12</v>
@@ -5871,10 +5938,10 @@
         <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5883,7 +5950,7 @@
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,7 +5959,7 @@
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
@@ -5954,43 +6021,43 @@
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J31" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M31" t="n">
         <v>24.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O31" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P31" t="n">
         <v>22.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.735</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
         <v>9</v>
       </c>
       <c r="S31" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V31" t="n">
         <v>14.4</v>
@@ -5999,7 +6066,7 @@
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
         <v>4.3</v>
@@ -6008,37 +6075,37 @@
         <v>20.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>104.2</v>
+        <v>103.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>18</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
         <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,7 +6114,7 @@
         <v>14</v>
       </c>
       <c r="AN31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
         <v>23</v>
@@ -6059,7 +6126,7 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS31" t="n">
         <v>22</v>
@@ -6077,16 +6144,16 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB31" t="n">
         <v>9</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-11-2015-16</t>
+          <t>2016-04-11</t>
         </is>
       </c>
     </row>
